--- a/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,3</t>
+          <t>-4,59; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,39</t>
+          <t>-4,51; 4,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 4,34</t>
+          <t>-5,38; 4,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,28</t>
+          <t>1,16; 9,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 113,16</t>
+          <t>-83,26; 122,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 83,68</t>
+          <t>-48,31; 94,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 78,72</t>
+          <t>-49,21; 72,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>219,69; 7275,54</t>
+          <t>232,03; 7548,73</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,41</t>
+          <t>-0,93; 5,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,45</t>
+          <t>-4,62; 1,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,79</t>
+          <t>-3,4; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,66</t>
+          <t>-5,72; 0,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 131,49</t>
+          <t>-15,7; 129,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 29,5</t>
+          <t>-52,51; 25,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 52,36</t>
+          <t>-38,77; 60,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 28,05</t>
+          <t>-71,8; 36,0</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,19</t>
+          <t>-5,49; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,9</t>
+          <t>-2,27; 4,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,3</t>
+          <t>0,13; 5,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,69</t>
+          <t>-4,66; 2,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 59,78</t>
+          <t>-56,31; 55,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 171,6</t>
+          <t>-48,97; 195,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 825,61</t>
+          <t>-18,94; 764,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 109,28</t>
+          <t>-65,75; 79,96</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,8</t>
+          <t>-1,39; 3,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,79</t>
+          <t>-3,76; 1,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,91</t>
+          <t>-6,69; 0,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,91</t>
+          <t>0,09; 1,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 337,85</t>
+          <t>-43,82; 315,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 70,57</t>
+          <t>-64,89; 63,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 18,49</t>
+          <t>-61,88; 20,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,14</t>
+          <t>-2,37; 6,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,86</t>
+          <t>-1,76; 6,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,66</t>
+          <t>-2,69; 3,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,76</t>
+          <t>0,19; 3,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 409,09</t>
+          <t>-51,86; 407,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 302,09</t>
+          <t>-37,54; 312,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 262,56</t>
+          <t>-65,52; 269,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,97</t>
+          <t>-1,16; 4,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,79</t>
+          <t>-0,54; 4,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,86</t>
+          <t>-2,29; 0,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,36</t>
+          <t>-2,06; 2,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,8; 773,16</t>
+          <t>-46,84; 681,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 579,88</t>
+          <t>-34,09; 581,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,31; 235,51</t>
+          <t>-71,25; 228,57</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,58</t>
+          <t>0,64; 6,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,45</t>
+          <t>1,88; 7,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,84</t>
+          <t>-1,48; 2,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,54</t>
+          <t>-3,31; 1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 173,33</t>
+          <t>7,94; 183,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,8; 219,11</t>
+          <t>30,51; 220,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 140,05</t>
+          <t>-33,79; 124,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 45,26</t>
+          <t>-65,71; 53,48</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,03</t>
+          <t>-2,86; 1,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,58</t>
+          <t>-0,28; 4,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,11</t>
+          <t>-0,91; 2,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,72</t>
+          <t>-0,61; 1,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,03; 46,86</t>
+          <t>-40,88; 39,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 146,42</t>
+          <t>-5,48; 135,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 159,96</t>
+          <t>-26,7; 158,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 497,89</t>
+          <t>-45,97; 458,86</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,26</t>
+          <t>-0,08; 2,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,45</t>
+          <t>0,3; 2,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,22</t>
+          <t>-0,74; 1,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,06</t>
+          <t>-0,74; 1,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 52,72</t>
+          <t>-1,31; 51,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 57,46</t>
+          <t>5,6; 59,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 32,01</t>
+          <t>-15,54; 35,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 59,69</t>
+          <t>-25,67; 63,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1312,49%</t>
+          <t>177,49%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,43</t>
+          <t>-4,77; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,81</t>
+          <t>-4,58; 4,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,46</t>
+          <t>-5,31; 4,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,63</t>
+          <t>0,13; 6,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 122,61</t>
+          <t>-81,27; 124,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 94,36</t>
+          <t>-49,37; 88,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,21; 72,72</t>
+          <t>-49,88; 71,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>232,03; 7548,73</t>
+          <t>-20,71; 1144,32</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-37,45%</t>
+          <t>-13,48%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,65</t>
+          <t>-0,88; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,31</t>
+          <t>-4,59; 1,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,85</t>
+          <t>-3,09; 2,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,76</t>
+          <t>-3,98; 2,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 129,42</t>
+          <t>-15,39; 128,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 25,65</t>
+          <t>-52,22; 28,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 60,68</t>
+          <t>-37,85; 55,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 36,0</t>
+          <t>-57,68; 75,66</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-12,74%</t>
+          <t>-1,93%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 2,92</t>
+          <t>-5,09; 3,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,32</t>
+          <t>-1,98; 4,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,18</t>
+          <t>0,36; 5,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,2</t>
+          <t>-3,61; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 55,15</t>
+          <t>-50,0; 65,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 195,52</t>
+          <t>-41,46; 188,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 764,26</t>
+          <t>-9,43; 818,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 79,96</t>
+          <t>-54,8; 102,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>656,03%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,87</t>
+          <t>-1,54; 3,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,75</t>
+          <t>-3,52; 2,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,97</t>
+          <t>-6,6; 0,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,82</t>
+          <t>-2,11; 1,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 315,03</t>
+          <t>-49,65; 311,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 63,14</t>
+          <t>-64,2; 81,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 20,09</t>
+          <t>-64,63; 20,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 6,33</t>
+          <t>-2,67; 6,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,51</t>
+          <t>-1,55; 6,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,58</t>
+          <t>-3,0; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,44</t>
+          <t>0,19; 1,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 407,38</t>
+          <t>-54,09; 369,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 312,28</t>
+          <t>-33,76; 296,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 269,99</t>
+          <t>-68,57; 328,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>-20,31%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,1</t>
+          <t>-1,4; 4,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,9</t>
+          <t>-0,56; 4,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,93</t>
+          <t>-2,24; 0,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,42</t>
+          <t>-3,2; 2,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 681,37</t>
+          <t>-58,41; 721,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 581,74</t>
+          <t>-35,0; 581,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,25; 228,57</t>
+          <t>-71,71; 132,43</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-13,04%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,67</t>
+          <t>0,85; 6,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,33</t>
+          <t>1,72; 7,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,78</t>
+          <t>-1,28; 2,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,73</t>
+          <t>-1,42; 3,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,94; 183,07</t>
+          <t>12,04; 192,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,51; 220,15</t>
+          <t>27,2; 212,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 124,79</t>
+          <t>-33,63; 130,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 53,48</t>
+          <t>-27,11; 97,23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,93</t>
+          <t>-2,92; 1,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,42</t>
+          <t>-0,2; 4,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,92</t>
+          <t>-0,76; 3,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,65</t>
+          <t>-0,41; 1,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 39,83</t>
+          <t>-40,93; 41,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 135,28</t>
+          <t>-3,87; 125,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 158,12</t>
+          <t>-21,94; 158,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 458,86</t>
+          <t>-35,13; 429,34</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,21</t>
+          <t>0,06; 2,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,51</t>
+          <t>0,21; 2,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,39</t>
+          <t>-0,78; 1,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,12</t>
+          <t>-0,29; 1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 51,23</t>
+          <t>1,01; 52,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,6; 59,0</t>
+          <t>3,55; 58,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 35,87</t>
+          <t>-16,12; 32,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 63,23</t>
+          <t>-9,19; 61,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
